--- a/out/MLP_Base_repeat_3_000006.xlsx
+++ b/out/MLP_Base_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5903981995424212</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.50126221553543</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5903981995424212</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003871177276349627</v>
+        <v>-0.0003217451348025352</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4982506704858836</v>
+        <v>0.4141108407685089</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9974442709128163</v>
+        <v>0.8290058003310873</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.115066559527235</v>
+        <v>-0.09563531163542903</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3827969932310136</v>
+        <v>0.3181537839982775</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.50126221553543</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3827969932310136</v>
+        <v>0.3181537839982775</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.50126221553543</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3823672355608861</v>
+        <v>0.317874030467744</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.320308343762333</v>
+        <v>0.8594633479055712</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.025613290775421</v>
+        <v>2.038512118685154</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2526261868985396</v>
+        <v>0.1644485653896632</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.901262215535431</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.208630264159415</v>
+        <v>1.50669180736866</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4424987249377066</v>
+        <v>0.288047258267752</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.901262215535431</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.841125362550363</v>
+        <v>1.91841868128348</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2423281663060954</v>
+        <v>0.1577451608387375</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.882902040021745</v>
+        <v>1.945613506873808</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.1000852585904828</v>
+        <v>0.06515124552584857</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.840489878416206</v>
+        <v>1.918004993962326</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1246971530454463</v>
+        <v>0.08117237060192903</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.989816706435402</v>
+        <v>2.015210406641441</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.07508438415217118</v>
+        <v>0.04887625232955294</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.015202720803305</v>
+        <v>2.031735657840622</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05708341874131721</v>
+        <v>0.03715998910605837</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.50126221553543</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.054254887122495</v>
+        <v>2.057157316612956</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02524893905579102</v>
+        <v>0.01643595988750051</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.047617202357171</v>
+        <v>2.052836472861554</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.02003522327707954</v>
+        <v>0.0130398794981484</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.062429616560102</v>
+        <v>2.062477793758531</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.00993338108611095</v>
+        <v>0.006463827960906852</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.901262215535431</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.062247241123653</v>
+        <v>2.06235732047787</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005772672680820269</v>
+        <v>0.003756596564098997</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.901262215535431</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.063856867191008</v>
+        <v>2.063403677172157</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002883836340410134</v>
+        <v>0.001877252882422313</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.063848270394753</v>
+        <v>2.063396333640256</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001423700136703706</v>
+        <v>0.0009235113564492899</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.063807104285882</v>
+        <v>2.063367794713835</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0008227378889198787</v>
+        <v>0.0005356997500202434</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.064031468093467</v>
+        <v>2.06351231826208</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002717642941325165</v>
+        <v>0.0001757895792317245</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.063750474081465</v>
+        <v>2.063327754979218</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001342390511308047</v>
+        <v>8.483164589084172e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.063747028629866</v>
+        <v>2.0633237628238</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.08320800333637e-05</v>
+        <v>4.392392260217012e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.063754574270378</v>
+        <v>2.063326927982303</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.292288715141218e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.901262215535431</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.063747091253211</v>
+        <v>2.063320299989562</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.827360596503633e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.901262215535431</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.063750696962403</v>
+        <v>2.063321218225707</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>2.732487839350877e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.50126221553543</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.063743027241308</v>
+        <v>2.063314215934886</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.50126221553543</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.063739542021</v>
+        <v>2.063310353859789</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.063734994708815</v>
+        <v>2.063305806547604</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.901262215535431</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.063735084653465</v>
+        <v>2.063305896492254</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.06373422671988</v>
+        <v>2.063305038558669</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.901262215535431</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.063734455040915</v>
+        <v>2.063305266879704</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.901262215535431</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.063733659376703</v>
+        <v>2.063304471215492</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.063733721646076</v>
+        <v>2.063304533484866</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.063733749321353</v>
+        <v>2.063304561160142</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.901262215535431</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.063733901535376</v>
+        <v>2.063304713374166</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.063733555594415</v>
+        <v>2.063304367433204</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.063733631701426</v>
+        <v>2.063304443540216</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.063733797753088</v>
+        <v>2.063304609591877</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.901262215535431</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.063734157531687</v>
+        <v>2.063304969370477</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.50126221553543</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.063734178288145</v>
+        <v>2.063304990126935</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.063734282070434</v>
+        <v>2.063305093909223</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5903981995424212</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.063734510391469</v>
+        <v>2.063305322230258</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.063734385852722</v>
+        <v>2.063305197691512</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.063734413528</v>
+        <v>2.063305225366789</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.901262215535431</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.063734468878553</v>
+        <v>2.063305280717342</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.063734731793684</v>
+        <v>2.063305543632473</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.063734648767853</v>
+        <v>2.063305460606642</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.063734441203276</v>
+        <v>2.063305253042066</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.063734455040915</v>
+        <v>2.063305266879704</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.063734593417299</v>
+        <v>2.063305405256089</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.063734309745711</v>
+        <v>2.0633051215845</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.06373413677523</v>
+        <v>2.063304948614019</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.063734032992942</v>
+        <v>2.063304844831731</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.063734178288145</v>
+        <v>2.063304990126935</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.063734420446819</v>
+        <v>2.063305232285608</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.063734247476338</v>
+        <v>2.063305059315127</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.063733949967111</v>
+        <v>2.0633047618059</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.063733936129472</v>
+        <v>2.063304747968262</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.063733569432053</v>
+        <v>2.063304381270842</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.063733569432053</v>
+        <v>2.063304381270842</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.06373350716268</v>
+        <v>2.063304319001469</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.063733403380391</v>
+        <v>2.063304215219181</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.06373323040991</v>
+        <v>2.0633040422487</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.063733278841645</v>
+        <v>2.063304090680434</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.063732919063045</v>
+        <v>2.063303730901834</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.06373287755013</v>
+        <v>2.063303689388919</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.063732932900683</v>
+        <v>2.063303744739473</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.063732988251238</v>
+        <v>2.063303800090027</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.063733029764153</v>
+        <v>2.063303841602942</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.063732759930203</v>
+        <v>2.063303571768992</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.063732815280757</v>
+        <v>2.063303627119546</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.06373296057596</v>
+        <v>2.06330377241475</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.063732925981864</v>
+        <v>2.063303737820654</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.063732912144226</v>
+        <v>2.063303723983015</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.190398199542421</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.063733002088876</v>
+        <v>2.063303813927665</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.50126221553543</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.06373332035456</v>
+        <v>2.06330413219335</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.06373314046526</v>
+        <v>2.06330395230405</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.063733181978176</v>
+        <v>2.063303993816965</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.063732995170057</v>
+        <v>2.063303807008846</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.063733064358249</v>
+        <v>2.063303876197038</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.063732863712492</v>
+        <v>2.063303675551281</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.063732905225407</v>
+        <v>2.063303717064196</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.190398199542421</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.063732932900683</v>
+        <v>2.063303744739473</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_3_000006.xlsx
+++ b/out/MLP_Base_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.4505587654005175</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.4505587654005175</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.05610647233156299</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.4505587654005175</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.05610647233156299</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636436</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003871177276349627</v>
+        <v>-0.0002916332056468818</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4982506704858836</v>
+        <v>0.3753546528009585</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9974442709128163</v>
+        <v>0.7514196571610892</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.115066559527235</v>
+        <v>-0.08668481762047078</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3827969932310136</v>
+        <v>0.2883782019748408</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3827969932310136</v>
+        <v>0.2883782019748408</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636436</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3823672355608861</v>
+        <v>0.2881448308046143</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.320308343762333</v>
+        <v>0.7169667059601319</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.025613290775421</v>
+        <v>1.723505891011588</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2526261868985396</v>
+        <v>0.1371835006529522</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636433</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.208630264159415</v>
+        <v>1.279859913762838</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4424987249377066</v>
+        <v>0.2402896940780898</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.841125362550363</v>
+        <v>1.623323483042589</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2423281663060954</v>
+        <v>0.1315916190242559</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.50126221553543</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.882902040021745</v>
+        <v>1.646009476367102</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.1000852585904828</v>
+        <v>0.05434905825224005</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.840489878416206</v>
+        <v>1.622978418808505</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1246971530454463</v>
+        <v>0.06771426266035155</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.989816706435402</v>
+        <v>1.704067596222689</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.07508438415217118</v>
+        <v>0.04077332352555252</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.015202720803305</v>
+        <v>1.717853048264876</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05708341874131721</v>
+        <v>0.03099778888262258</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636436</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.054254887122495</v>
+        <v>1.739059677029237</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02524893905579102</v>
+        <v>0.01371059052580104</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.05610647233156299</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.047617202357171</v>
+        <v>1.735454538661493</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.02003522327707954</v>
+        <v>0.01087834397418993</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.05610647233156299</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.062429616560102</v>
+        <v>1.74349668566174</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.00993338108611095</v>
+        <v>0.005390692927948986</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636435</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.062247241123653</v>
+        <v>1.743395365178018</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005772672680820269</v>
+        <v>0.003134027604534275</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.063856867191008</v>
+        <v>1.744267374779088</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002883836340410134</v>
+        <v>0.001563059201894323</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.063848270394753</v>
+        <v>1.74426042243953</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001423700136703706</v>
+        <v>0.0007711550038430596</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.063807104285882</v>
+        <v>1.744235774855234</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0008227378889198787</v>
+        <v>0.0004455831250168694</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.064031468093467</v>
+        <v>1.744355377812104</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002717642941325165</v>
+        <v>0.0001445419976361178</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.063750474081465</v>
+        <v>1.744200743147301</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001342390511308047</v>
+        <v>7.135689900721546e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636436</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.063747028629866</v>
+        <v>1.744196588053204</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.08320800333637e-05</v>
+        <v>3.658533421184461e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.063754574270378</v>
+        <v>1.744198357889037</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.292288715141218e-05</v>
+        <v>1.396144357570609e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636433</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.063747091253211</v>
+        <v>1.744192040273442</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.827360596503633e-05</v>
+        <v>6.636802982518164e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.063750696962403</v>
+        <v>1.744191882795938</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.50126221553543</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.063743027241308</v>
+        <v>1.744185215832068</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636436</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.063739542021</v>
+        <v>1.744181353756972</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.7627717100636435</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.063734994708815</v>
+        <v>1.744176806444786</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156302</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.063735084653465</v>
+        <v>1.744176896389436</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.7627717100636435</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.06373422671988</v>
+        <v>1.744176038455851</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636435</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.063734455040915</v>
+        <v>1.744176266776886</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636435</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.063733659376703</v>
+        <v>1.744175471112674</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.05610647233156306</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.063733721646076</v>
+        <v>1.744175533382047</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.05610647233156306</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.063733749321353</v>
+        <v>1.744175561057325</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156306</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.063733901535376</v>
+        <v>1.744175713271347</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.05610647233156306</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.063733555594415</v>
+        <v>1.744175367330386</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.063733631701426</v>
+        <v>1.744175443437397</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.05610647233156299</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.063733797753088</v>
+        <v>1.744175609489059</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636435</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.063734157531687</v>
+        <v>1.744175969267659</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.063734178288145</v>
+        <v>1.744175990024117</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636436</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.063734282070434</v>
+        <v>1.744176093806405</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.2561064723315631</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.063734510391469</v>
+        <v>1.74417632212744</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.063734385852722</v>
+        <v>1.744176197588694</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.05610647233156299</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.063734413528</v>
+        <v>1.744176225263971</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156302</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.063734468878553</v>
+        <v>1.744176280614525</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.05610647233156302</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.063734731793684</v>
+        <v>1.744176543529655</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.063734648767853</v>
+        <v>1.744176460503825</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.063734441203276</v>
+        <v>1.744176252939247</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.063734455040915</v>
+        <v>1.744176266776886</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.063734593417299</v>
+        <v>1.744176405153271</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.063734309745711</v>
+        <v>1.744176121481682</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.06373413677523</v>
+        <v>1.744175948511201</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.063734032992942</v>
+        <v>1.744175844728913</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.063734178288145</v>
+        <v>1.744175990024117</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.063734420446819</v>
+        <v>1.74417623218279</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.063734247476338</v>
+        <v>1.744176059212309</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.063733949967111</v>
+        <v>1.744175761703082</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.063733936129472</v>
+        <v>1.744175747865444</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.063733569432053</v>
+        <v>1.744175381168024</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.063733569432053</v>
+        <v>1.744175381168024</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.06373350716268</v>
+        <v>1.744175318898651</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.063733403380391</v>
+        <v>1.744175215116363</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.06373323040991</v>
+        <v>1.744175042145882</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.063733278841645</v>
+        <v>1.744175090577616</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.063732919063045</v>
+        <v>1.744174730799017</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.06373287755013</v>
+        <v>1.744174689286101</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.063732932900683</v>
+        <v>1.744174744636655</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.063732988251238</v>
+        <v>1.744174799987209</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.063733029764153</v>
+        <v>1.744174841500124</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.063732759930203</v>
+        <v>1.744174571666174</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.063732815280757</v>
+        <v>1.744174627016728</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.06373296057596</v>
+        <v>1.744174772311932</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.063732925981864</v>
+        <v>1.744174737717836</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.063732912144226</v>
+        <v>1.744174723880197</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.063733002088876</v>
+        <v>1.744174813824847</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.06373332035456</v>
+        <v>1.744175132090532</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.06373314046526</v>
+        <v>1.744174952201232</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.4505587654005175</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.063733181978176</v>
+        <v>1.744174993714147</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.4505587654005175</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.063732995170057</v>
+        <v>1.744174806906028</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.063733064358249</v>
+        <v>1.74417487609422</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.063732863712492</v>
+        <v>1.744174675448463</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.063732905225407</v>
+        <v>1.744174716961378</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6505587654005176</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.063732932900683</v>
+        <v>1.744174744636655</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_3_000006.xlsx
+++ b/out/MLP_Base_repeat_3_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4161360263824463</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4174140393733978</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9299999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4340641796588898</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4611026048660278</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4159396588802338</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4415827393531799</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3916065096855164</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4499716758728027</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4562448859214783</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4158073961734772</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.3944039344787598</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3740265071392059</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4228576719760895</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3829045295715332</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.3757911324501038</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.3724560439586639</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4014962017536163</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6505587654005176</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4241060018539429</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6505587654005176</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4661745131015778</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6505587654005176</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4186697602272034</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6505587654005176</v>
+        <v>0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4028057157993317</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6505587654005176</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3799417614936829</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3859449923038483</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4483402371406555</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3929602801799774</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4766936004161835</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.256106472331563</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.552507221698761</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.256106472331563</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.496635228395462</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.256106472331563</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4496955275535583</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4505587654005175</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4555481672286987</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4505587654005175</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4040273427963257</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6505587654005176</v>
+        <v>0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3824445009231567</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4056586027145386</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.05610647233156299</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5083146095275879</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.456125408411026</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.256106472331563</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4479032456874847</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4505587654005175</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.478863388299942</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6505587654005176</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4257285296916962</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6505587654005176</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4432025849819183</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6505587654005176</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4802363514900208</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.05610647233156299</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5250826478004456</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9627717100636436</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5482648015022278</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6119739413261414</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002916332056468818</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3753546528009585</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.5916216373443604</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7514196571610892</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08668481762047078</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5094715356826782</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.669436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2883782019748408</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5511494278907776</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.669436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2883782019748408</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5480727553367615</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9627717100636436</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2881448308046143</v>
+        <v>0.2122727167830646</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.7169667059601319</v>
+        <v>0.3661950314083699</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4981088936328888</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.9627717100636434</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.723505891011588</v>
+        <v>0.9453922846818488</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1371835006529522</v>
+        <v>0.07006735519795214</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.572519838809967</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7627717100636433</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.279859913762838</v>
+        <v>0.718797248674785</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2402896940780898</v>
+        <v>0.1227294001466499</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5495274066925049</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.623323483042589</v>
+        <v>0.8942234757282896</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1315916190242559</v>
+        <v>0.06721132397827324</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.5599827170372009</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.469436947795724</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.646009476367102</v>
+        <v>0.9058105027624485</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.05434905825224005</v>
+        <v>0.02775905880951137</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5279130935668945</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.669436947795724</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.622978418808505</v>
+        <v>0.8940472319822265</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.06771426266035155</v>
+        <v>0.03458540515472364</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.6319524645805359</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.669436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.704067596222689</v>
+        <v>0.935464230815531</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04077332352555252</v>
+        <v>0.02082547197424655</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.5299682021141052</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.669436947795724</v>
+        <v>-0.16</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.717853048264876</v>
+        <v>0.9425053184761174</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03099778888262258</v>
+        <v>0.01583205915755942</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.6801860332489014</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9627717100636436</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.739059677029237</v>
+        <v>0.9533368633026545</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01371059052580104</v>
+        <v>0.007000599424997798</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4446746706962585</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.05610647233156299</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.735454538661493</v>
+        <v>0.951492997726175</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01087834397418993</v>
+        <v>0.005553954836411267</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3404187262058258</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.05610647233156299</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.74349668566174</v>
+        <v>0.9555982901916548</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.005390692927948986</v>
+        <v>0.002751631250162162</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.7627636194229126</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7627717100636435</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.743395365178018</v>
+        <v>0.9555440911654862</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003134027604534275</v>
+        <v>0.001597969610841877</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.7525635957717896</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.744267374779088</v>
+        <v>0.9559869431489801</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001563059201894323</v>
+        <v>0.0007950302050481237</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.6256611347198486</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.669436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.74426042243953</v>
+        <v>0.9559809470573687</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0007711550038430596</v>
+        <v>0.0003917014464086749</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.6120004653930664</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.669436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.744235774855234</v>
+        <v>0.9559659049587285</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0004455831250168694</v>
+        <v>0.0002252980416752888</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.6379709243774414</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.669436947795724</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.744355377812104</v>
+        <v>0.9560245909144622</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001445419976361178</v>
+        <v>7.088698387504487e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.5399271845817566</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.669436947795724</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.744200743147301</v>
+        <v>0.9559431116611959</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>7.135689900721546e-05</v>
+        <v>3.317844950360773e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.5456794500350952</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9627717100636436</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.744196588053204</v>
+        <v>0.9559385479517856</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>3.658533421184461e-05</v>
+        <v>1.701576517097656e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.4952737390995026</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9627717100636434</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.744198357889037</v>
+        <v>0.9559371319825209</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.396144357570609e-05</v>
+        <v>4.480721787853046e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.544810950756073</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7627717100636433</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.744192040273442</v>
+        <v>0.9559314351212175</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.5722546577453613</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.744191882795938</v>
+        <v>0.9559291262164156</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.5456891059875488</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.744185215832068</v>
+        <v>0.9559231266828189</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.5824687480926514</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9627717100636436</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.744181353756972</v>
+        <v>0.9559188840726649</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4848403036594391</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7627717100636435</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.744176806444786</v>
+        <v>0.9559191123936995</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.5029264092445374</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.05610647233156302</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.744176896389436</v>
+        <v>0.9559192023383496</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.4867542088031769</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7627717100636435</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.744176038455851</v>
+        <v>0.9559183444047648</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.5247018337249756</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7627717100636435</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.744176266776886</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.5403764843940735</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7627717100636435</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.744175471112674</v>
+        <v>0.9559177770615876</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4544408917427063</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.05610647233156306</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.744175533382047</v>
+        <v>0.9559178393309608</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.471104234457016</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.05610647233156306</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.744175561057325</v>
+        <v>0.9559178670062376</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.5158376693725586</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.05610647233156306</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.744175713271347</v>
+        <v>0.9559180192202609</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4525779187679291</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.05610647233156306</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.744175367330386</v>
+        <v>0.9559176732792992</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.470382034778595</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.744175443437397</v>
+        <v>0.9559177493863108</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4097653329372406</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.05610647233156299</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.744175609489059</v>
+        <v>0.9559179154379724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.5091848969459534</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7627717100636435</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.744175969267659</v>
+        <v>0.9559182752165725</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5400905609130859</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.669436947795724</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.744175990024117</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.5686745047569275</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9627717100636436</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.744176093806405</v>
+        <v>0.9559183997553187</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.470304936170578</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2561064723315631</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.74417632212744</v>
+        <v>0.9559186280763533</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4361862242221832</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.744176197588694</v>
+        <v>0.9559185035376071</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3928329050540924</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.05610647233156299</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.744176225263971</v>
+        <v>0.9559185312128839</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.5093913674354553</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.05610647233156302</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.744176280614525</v>
+        <v>0.955918586563438</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.4370101392269135</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.05610647233156302</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.744176543529655</v>
+        <v>0.9559188494785686</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.444550633430481</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.744176460503825</v>
+        <v>0.9559187664527379</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4197699129581451</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.744176252939247</v>
+        <v>0.9559185588881611</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4097206294536591</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.744176266776886</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.4003520905971527</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.744176405153271</v>
+        <v>0.9559187111021842</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3953864872455597</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.744176121481682</v>
+        <v>0.9559184274305955</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3789852559566498</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.744175948511201</v>
+        <v>0.9559182544601148</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4568876922130585</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.744175844728913</v>
+        <v>0.9559181506778263</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4156983494758606</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.744175990024117</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3826042115688324</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.74417623218279</v>
+        <v>0.9559185381317034</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3924280405044556</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.744176059212309</v>
+        <v>0.9559183651612224</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3747624754905701</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.744175761703082</v>
+        <v>0.9559180676519955</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3995905220508575</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.744175747865444</v>
+        <v>0.9559180538143569</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3858662247657776</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.744175381168024</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4167535603046417</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.744175381168024</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4743916094303131</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.744175318898651</v>
+        <v>0.9559176248475646</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3923533856868744</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.744175215116363</v>
+        <v>0.9559175210652762</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4032668173313141</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.744175042145882</v>
+        <v>0.9559173480947953</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4140903055667877</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.744175090577616</v>
+        <v>0.95591739652653</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4024111330509186</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.744174730799017</v>
+        <v>0.9559170367479298</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.389228880405426</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.744174689286101</v>
+        <v>0.9559169952350145</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4285033047199249</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.744174744636655</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.372420459985733</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.744174799987209</v>
+        <v>0.9559171059361221</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.379132479429245</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.744174841500124</v>
+        <v>0.9559171474490376</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3805489242076874</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.744174571666174</v>
+        <v>0.9559168776150875</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3891459703445435</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.744174627016728</v>
+        <v>0.9559169329656414</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3750188946723938</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.744174772311932</v>
+        <v>0.9559170782608453</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3810556530952454</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.744174737717836</v>
+        <v>0.955917043666749</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.369391918182373</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6505587654005176</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.744174723880197</v>
+        <v>0.9559170298291105</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4585517346858978</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.744174813824847</v>
+        <v>0.9559171197737607</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.559475302696228</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.256106472331563</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.744175132090532</v>
+        <v>0.9559174380394453</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4573913812637329</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.256106472331563</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.744174952201232</v>
+        <v>0.9559172581501452</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4390491247177124</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4505587654005175</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.744174993714147</v>
+        <v>0.9559172996630606</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4382262825965881</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4505587654005175</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.744174806906028</v>
+        <v>0.9559171128549413</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3943383991718292</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6505587654005176</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.74417487609422</v>
+        <v>0.9559171820431338</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4242722690105438</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.744174675448463</v>
+        <v>0.9559169813973759</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3923476338386536</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.744174716961378</v>
+        <v>0.9559170229102913</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4210987985134125</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6505587654005176</v>
+        <v>-0.7200000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.744174744636655</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_3_000006.xlsx
+++ b/out/MLP_Base_repeat_3_000006.xlsx
@@ -50234,7 +50234,7 @@
         <v>0.6120004653930664</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
         <v>0.9559659049587285</v>
@@ -51029,7 +51029,7 @@
         <v>0.6379709243774414</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0.9560245909144622</v>
@@ -51824,7 +51824,7 @@
         <v>0.5399271845817566</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
         <v>0.9559431116611959</v>
@@ -52619,7 +52619,7 @@
         <v>0.5456794500350952</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0.9559385479517856</v>
@@ -53414,7 +53414,7 @@
         <v>0.4952737390995026</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0.9559371319825209</v>
@@ -54209,7 +54209,7 @@
         <v>0.544810950756073</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0.9559314351212175</v>
@@ -55004,7 +55004,7 @@
         <v>0.5722546577453613</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>0.9559291262164156</v>
@@ -55799,7 +55799,7 @@
         <v>0.5456891059875488</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>0.9559231266828189</v>
